--- a/out/07_Ops/SNX-OPS-FRM-04 Change Request Approval Log (Rev00 DRAFT).xlsx
+++ b/out/07_Ops/SNX-OPS-FRM-04 Change Request Approval Log (Rev00 DRAFT).xlsx
@@ -14,7 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Change Log'!$A$4:$U$155</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Change Log'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Ringkasan'!$6:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -177,7 +180,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -331,6 +334,45 @@
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -732,8 +774,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="28">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="3" s="28">
+      <c r="A3" s="52" t="n"/>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="28">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -743,9 +792,12 @@
           <t>SNX-OPS-FRM-04</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="28">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="C4" s="52" t="n"/>
+      <c r="D4" s="52" t="n"/>
+      <c r="E4" s="52" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="28">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -755,9 +807,12 @@
           <t>Change Request &amp; Approval Log</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="28">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="C5" s="52" t="n"/>
+      <c r="D5" s="52" t="n"/>
+      <c r="E5" s="52" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="28">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -767,9 +822,12 @@
           <t>00 (DRAFT)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="C6" s="52" t="n"/>
+      <c r="D6" s="52" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -779,9 +837,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="52" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -791,9 +852,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="28">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="28">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -803,9 +867,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="28">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="28">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -815,9 +882,12 @@
           <t>Head of Operation</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="28">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="28">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -827,9 +897,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="28">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="28">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -839,9 +912,12 @@
           <t>Klausul 8.5.6</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="28">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="28">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -851,9 +927,12 @@
           <t>Kontrol Annex A 8.32</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="28">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="28">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -863,64 +942,90 @@
           <t>3 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="28">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="28">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Log seluruh change request proyek dan teknis beserta approval, eksekusi, dan hasilnya sesuai SNX-OPS-SOP-02.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="28">
-      <c r="A17" s="33" t="inlineStr">
+          <t>Log semua change request proyek dan teknis, lengkap dengan approval, eksekusi, dan hasilnya, sesuai SNX-OPS-SOP-02.</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
+    </row>
+    <row r="16" s="28">
+      <c r="A16" s="52" t="n"/>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="52" t="n"/>
+      <c r="E16" s="52" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="28">
+      <c r="A17" s="54" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="23.85" customHeight="1" s="28">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+      <c r="E17" s="52" t="n"/>
+    </row>
+    <row r="18" ht="43.5" customHeight="1" s="28">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Satu nomor CR per perubahan: CR-YYYY-NNNN. CR juga dibuat sebagai tiket di Zammad (USULAN); log ini menjadi rekap audit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="28">
-      <c r="A19" s="34" t="inlineStr">
+          <t>Gunakan satu nomor CR untuk satu perubahan, dengan format CR-YYYY-NNNN. Log ini menjadi rekap audit, sedangkan CR juga dibuat sebagai ticket di Zammad (USULAN).</t>
+        </is>
+      </c>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+      <c r="E18" s="52" t="n"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1" s="28">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Kolom Go-gate otomatis CEK bila backup, rollback, atau approval belum lengkap (kecuali Emergency).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="28">
-      <c r="A20" s="34" t="inlineStr">
+          <t>Kolom Go-gate otomatis bernilai CEK jika backup, rollback, atau approval belum lengkap, kecuali untuk change Emergency.</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+      <c r="E19" s="52" t="n"/>
+    </row>
+    <row r="20" ht="43.5" customHeight="1" s="28">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Kolom PIR otomatis Ya untuk change Major atau yang berakhir rollback; tinjau dalam 5 hari kerja.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="28">
-      <c r="A21" s="34" t="inlineStr">
+          <t>Kolom PIR otomatis bernilai Ya untuk change Major atau change yang berakhir rollback. Lakukan PIR dalam 5 hari kerja.</t>
+        </is>
+      </c>
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="28">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
@@ -930,73 +1035,107 @@
           <t>Sheet Ringkasan menghitung statistik per jenis change untuk laporan KPI bulanan.</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="28">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+      <c r="E21" s="52" t="n"/>
+    </row>
+    <row r="22" s="28">
+      <c r="A22" s="52" t="n"/>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+      <c r="E22" s="52" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="28">
+      <c r="A23" s="54" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="28">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="28">
+      <c r="A24" s="55" t="n"/>
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="28">
-      <c r="A25" s="37" t="n"/>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="28">
+      <c r="A25" s="56" t="n"/>
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Biru muda: warna baris contoh, sudah dikosongkan dan tidak dipakai</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="28">
-      <c r="A26" s="38" t="n"/>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="28">
+      <c r="A26" s="57" t="n"/>
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="28">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="C26" s="52" t="n"/>
+      <c r="D26" s="52" t="n"/>
+      <c r="E26" s="52" t="n"/>
+    </row>
+    <row r="27" s="28">
+      <c r="A27" s="52" t="n"/>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+      <c r="E27" s="52" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="28">
+      <c r="A28" s="54" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="28">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="B28" s="52" t="n"/>
+      <c r="C28" s="52" t="n"/>
+      <c r="D28" s="52" t="n"/>
+      <c r="E28" s="52" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="28">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B29" s="39" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C29" s="39" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D29" s="39" t="inlineStr">
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E29" s="39" t="inlineStr">
+      <c r="E29" s="43" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="23.85" customHeight="1" s="28">
+    <row r="30" ht="30" customHeight="1" s="28">
       <c r="A30" s="32" t="inlineStr">
         <is>
           <t>00</t>
@@ -1030,76 +1169,91 @@
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="32" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="28">
-      <c r="A33" s="33" t="inlineStr">
+    <row r="32" s="28">
+      <c r="A32" s="52" t="n"/>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+      <c r="E32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="28">
+      <c r="A33" s="54" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="28">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+      <c r="E33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="28">
+      <c r="A34" s="43" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B34" s="39" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C34" s="39" t="inlineStr">
+      <c r="C34" s="43" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D34" s="39" t="inlineStr">
+      <c r="D34" s="43" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E34" s="52" t="n"/>
     </row>
     <row r="35" ht="27.75" customHeight="1" s="28">
-      <c r="A35" s="40" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C35" s="40" t="n"/>
-      <c r="D35" s="40" t="n"/>
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="52" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="28">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C36" s="40" t="n"/>
-      <c r="D36" s="40" t="n"/>
+      <c r="C36" s="32" t="n"/>
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="52" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="28">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C37" s="40" t="n"/>
-      <c r="D37" s="40" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="n"/>
+      <c r="E37" s="52" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1143,130 +1297,137 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="27" min="1" max="4"/>
+    <col width="13" customWidth="1" style="28" min="2" max="2"/>
+    <col width="13" customWidth="1" style="28" min="3" max="3"/>
+    <col width="13" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="28">
-      <c r="A1" s="42" t="inlineStr">
+    <row r="1" ht="16.5" customHeight="1" s="28">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>Jenis</t>
         </is>
       </c>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="58" t="inlineStr">
         <is>
           <t>Approval</t>
         </is>
       </c>
-      <c r="C1" s="42" t="inlineStr">
+      <c r="C1" s="58" t="inlineStr">
         <is>
           <t>Ack</t>
         </is>
       </c>
-      <c r="D1" s="42" t="inlineStr">
+      <c r="D1" s="58" t="inlineStr">
         <is>
           <t>Hasil</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="28">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="28">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>Standar</t>
         </is>
       </c>
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>Menunggu</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="59" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="D2" s="34" t="inlineStr">
+      <c r="D2" s="59" t="inlineStr">
         <is>
           <t>Berhasil</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="28">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="28">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="59" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="59" t="inlineStr">
         <is>
           <t>Rollback</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="28">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="28">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="59" t="inlineStr">
         <is>
           <t>Ditolak</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="59" t="inlineStr">
         <is>
           <t>Tidak perlu</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>Gagal</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="28">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="28">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>Emergency</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="C5" s="60" t="n"/>
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>Dibatalkan</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="28">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="28">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>Proyek</t>
         </is>
       </c>
+      <c r="B6" s="60" t="n"/>
+      <c r="C6" s="60" t="n"/>
+      <c r="D6" s="60" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1290,13 +1451,15 @@
     <col width="18" customWidth="1" style="27" min="9" max="9"/>
     <col width="20" customWidth="1" style="27" min="10" max="10"/>
     <col width="14" customWidth="1" style="27" min="11" max="11"/>
-    <col width="11" customWidth="1" style="27" min="12" max="13"/>
-    <col width="9" customWidth="1" style="27" min="14" max="14"/>
+    <col width="12" customWidth="1" style="27" min="12" max="13"/>
+    <col width="13" customWidth="1" style="28" min="13" max="13"/>
+    <col width="14" customWidth="1" style="27" min="14" max="14"/>
     <col width="15" customWidth="1" style="27" min="15" max="15"/>
     <col width="14" customWidth="1" style="27" min="16" max="16"/>
     <col width="11" customWidth="1" style="27" min="17" max="17"/>
     <col width="15" customWidth="1" style="27" min="18" max="18"/>
-    <col width="8" customWidth="1" style="27" min="19" max="20"/>
+    <col width="11" customWidth="1" style="27" min="19" max="20"/>
+    <col width="13" customWidth="1" style="28" min="20" max="20"/>
     <col width="22" customWidth="1" style="27" min="21" max="21"/>
   </cols>
   <sheetData>
@@ -5844,7 +6007,7 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -5852,13 +6015,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="27" min="1" max="1"/>
     <col width="14" customWidth="1" style="27" min="2" max="6"/>
+    <col width="13" customWidth="1" style="28" min="3" max="3"/>
+    <col width="13" customWidth="1" style="28" min="4" max="4"/>
+    <col width="13" customWidth="1" style="28" min="5" max="5"/>
+    <col width="13" customWidth="1" style="28" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="28">
@@ -5871,7 +6038,7 @@
     <row r="2" ht="15" customHeight="1" s="28">
       <c r="A2" s="48" t="inlineStr">
         <is>
-          <t>Isi periode di B3 dan B4; seluruh angka dihitung dari sheet Change Log berdasarkan Tanggal ajukan.</t>
+          <t>Isi periode di sel B3 dan B4. Semua angka dihitung dari sheet Change Log berdasarkan Tanggal ajukan.</t>
         </is>
       </c>
     </row>
@@ -5895,7 +6062,7 @@
         <v>46356</v>
       </c>
     </row>
-    <row r="6" ht="23.85" customHeight="1" s="28">
+    <row r="6" ht="57" customHeight="1" s="28">
       <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Jenis</t>
@@ -5927,186 +6094,186 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="40" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>Standar</t>
         </is>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A7,'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A7,'Change Log'!$Q$5:$Q$155,"Berhasil",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A7,'Change Log'!$Q$5:$Q$155,"Rollback",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A7,'Change Log'!$Q$5:$Q$155,"Gagal",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="62">
         <f>IF(B7=0,"",1-D7/B7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="A8" s="40" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A8,'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A8,'Change Log'!$Q$5:$Q$155,"Berhasil",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A8,'Change Log'!$Q$5:$Q$155,"Rollback",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A8,'Change Log'!$Q$5:$Q$155,"Gagal",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="F8" s="50">
+      <c r="F8" s="62">
         <f>IF(B8=0,"",1-D8/B8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="28">
-      <c r="A9" s="40" t="inlineStr">
+    <row r="9" ht="16.5" customHeight="1" s="28">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A9,'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A9,'Change Log'!$Q$5:$Q$155,"Berhasil",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A9,'Change Log'!$Q$5:$Q$155,"Rollback",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A9,'Change Log'!$Q$5:$Q$155,"Gagal",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="62">
         <f>IF(B9=0,"",1-D9/B9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="28">
-      <c r="A10" s="40" t="inlineStr">
+    <row r="10" ht="16.5" customHeight="1" s="28">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>Emergency</t>
         </is>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A10,'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A10,'Change Log'!$Q$5:$Q$155,"Berhasil",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A10,'Change Log'!$Q$5:$Q$155,"Rollback",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A10,'Change Log'!$Q$5:$Q$155,"Gagal",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="62">
         <f>IF(B10=0,"",1-D10/B10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="28">
-      <c r="A11" s="40" t="inlineStr">
+    <row r="11" ht="16.5" customHeight="1" s="28">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>Proyek</t>
         </is>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A11,'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A11,'Change Log'!$Q$5:$Q$155,"Berhasil",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A11,'Change Log'!$Q$5:$Q$155,"Rollback",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="61">
         <f>COUNTIFS('Change Log'!$F$5:$F$155,A11,'Change Log'!$Q$5:$Q$155,"Gagal",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="62">
         <f>IF(B11=0,"",1-D11/B11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="28">
-      <c r="A12" s="31" t="inlineStr">
+    <row r="12" ht="16.5" customHeight="1" s="28">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="63">
         <f>SUM(B7:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="63">
         <f>SUM(C7:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="63">
         <f>SUM(D7:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="63">
         <f>SUM(E7:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="64">
         <f>IF(B12=0,"",1-D12/B12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="28">
-      <c r="A13" s="40" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="28">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>CR dieksekusi tanpa go-gate lengkap (status CEK)</t>
         </is>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="61">
         <f>COUNTIFS('Change Log'!$S$5:$S$155,"CEK",'Change Log'!$B$5:$B$155,"&gt;="&amp;$B$3,'Change Log'!$B$5:$B$155,"&lt;="&amp;$B$4)</f>
         <v/>
       </c>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="40" t="n"/>
-      <c r="E13" s="40" t="n"/>
-      <c r="F13" s="50" t="n"/>
+      <c r="C13" s="61" t="n"/>
+      <c r="D13" s="61" t="n"/>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="62" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/out/07_Ops/SNX-OPS-FRM-04 Change Request Approval Log (Rev00 DRAFT).xlsx
+++ b/out/07_Ops/SNX-OPS-FRM-04 Change Request Approval Log (Rev00 DRAFT).xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Gunakan satu nomor CR untuk satu perubahan, dengan format CR-YYYY-NNNN. Log ini menjadi rekap audit, sedangkan CR juga dibuat sebagai ticket di Zammad (USULAN).</t>
+          <t>Gunakan satu nomor CR untuk satu perubahan, dengan format CR-YYYY-NNNN. CR juga dibuat sebagai ticket di Zammad (USULAN). Log ini menjadi rekap audit.</t>
         </is>
       </c>
       <c r="C18" s="52" t="n"/>
